--- a/Data/output.xlsx
+++ b/Data/output.xlsx
@@ -452,14 +452,14 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>0.118583725331659</v>
+        <v>72.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
@@ -471,14 +471,14 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02664716777316201</v>
+        <v>52.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
@@ -490,10 +490,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4113681588156692</v>
+        <v>55.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -509,14 +509,14 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4708189283640429</v>
+        <v>71.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
@@ -528,14 +528,14 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05873207919422485</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
@@ -547,14 +547,14 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3360538625936538</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
@@ -566,14 +566,14 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2326531828285703</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
@@ -585,10 +585,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2214272877704803</v>
+        <v>63.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7725815329216053</v>
+        <v>81</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
@@ -623,14 +623,14 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06935579542186932</v>
+        <v>62</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
@@ -642,14 +642,14 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2839750858548881</v>
+        <v>62.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
@@ -661,14 +661,14 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8409842849062504</v>
+        <v>94.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
@@ -680,14 +680,14 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05599469230673304</v>
+        <v>76.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="1" t="n">
@@ -699,14 +699,14 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2024962341579589</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="1" t="n">
@@ -718,10 +718,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>0.671834592471071</v>
+        <v>61.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -737,14 +737,14 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4316964037069261</v>
+        <v>61.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
@@ -756,10 +756,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2796739816016849</v>
+        <v>54.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -775,10 +775,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5032701938223981</v>
+        <v>69.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2473050381665327</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04111073936855658</v>
+        <v>60.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
@@ -832,14 +832,14 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6299592170503066</v>
+        <v>67.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" s="1" t="n">
@@ -851,14 +851,14 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5584336179014622</v>
+        <v>96.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="1" t="n">
@@ -870,10 +870,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5781637266678801</v>
+        <v>57.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -889,14 +889,14 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2335573506972434</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="1" t="n">
@@ -908,14 +908,14 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3639422269808629</v>
+        <v>86.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="1" t="n">
@@ -927,14 +927,14 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9330258919145342</v>
+        <v>81</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
@@ -946,10 +946,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4148777242908888</v>
+        <v>56.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -965,14 +965,14 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7276071579446324</v>
+        <v>90.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="1" t="n">
@@ -984,14 +984,14 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3193038075616657</v>
+        <v>79.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="1" t="n">
@@ -1003,14 +1003,14 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2616760376787874</v>
+        <v>58.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" s="1" t="n">
@@ -1022,10 +1022,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9497477255560611</v>
+        <v>60</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1041,14 +1041,14 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9350491032418908</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" s="1" t="n">
@@ -1060,14 +1060,14 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4622853143678687</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
@@ -1079,14 +1079,14 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3629578976448032</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
@@ -1098,14 +1098,14 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>0.05456395990832252</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
@@ -1117,14 +1117,14 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6157597317431174</v>
+        <v>82.7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
@@ -1136,14 +1136,14 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3523756847723292</v>
+        <v>63.7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
@@ -1155,14 +1155,14 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9908645068808306</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
@@ -1174,10 +1174,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7789007519377401</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C41" t="n">
-        <v>0.459691849869631</v>
+        <v>53.1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1212,14 +1212,14 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1624501593748482</v>
+        <v>98.2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
@@ -1231,14 +1231,14 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9784576652300924</v>
+        <v>80.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
@@ -1250,14 +1250,14 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5192631260150461</v>
+        <v>92.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
@@ -1269,14 +1269,14 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6279550941915061</v>
+        <v>80.5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
@@ -1288,14 +1288,14 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7306435424296629</v>
+        <v>61.8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="1" t="n">
@@ -1307,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>0.05024628775522244</v>
+        <v>71.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1326,14 +1326,14 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C48" t="n">
-        <v>0.729747860834199</v>
+        <v>52.6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="1" t="n">
@@ -1345,14 +1345,14 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6353809574552736</v>
+        <v>54.1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="1" t="n">
@@ -1364,14 +1364,14 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9063608340459391</v>
+        <v>77.7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="1" t="n">
@@ -1383,14 +1383,14 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9806174723525068</v>
+        <v>85.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E51" s="1" t="n">
@@ -1402,14 +1402,14 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6387429682218846</v>
+        <v>95.7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="1" t="n">
@@ -1421,14 +1421,14 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1482953869375291</v>
+        <v>77.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E53" s="1" t="n">
@@ -1440,14 +1440,14 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1889904887893153</v>
+        <v>85.8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
@@ -1459,14 +1459,14 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5805636259825054</v>
+        <v>65.7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
@@ -1478,10 +1478,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1942098025005542</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03326814783122267</v>
+        <v>70.2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1516,14 +1516,14 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8343277258340043</v>
+        <v>84.2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
@@ -1535,14 +1535,14 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5740223079940253</v>
+        <v>87.3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
@@ -1554,14 +1554,14 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5253207155999922</v>
+        <v>55.1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
@@ -1573,14 +1573,14 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1471289082370346</v>
+        <v>53.4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
@@ -1592,14 +1592,14 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4366286323683674</v>
+        <v>62.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
@@ -1611,10 +1611,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2857887738538634</v>
+        <v>59.9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7808721864367767</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C65" t="n">
-        <v>0.3599644651864446</v>
+        <v>60.8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
@@ -1668,14 +1668,14 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3035977605310148</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
@@ -1687,14 +1687,14 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6103841943970851</v>
+        <v>92.8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
@@ -1706,14 +1706,14 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1526683655082673</v>
+        <v>83.5</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
@@ -1725,10 +1725,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6275936178664633</v>
+        <v>82.7</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1744,14 +1744,14 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8593167757074238</v>
+        <v>56.6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
@@ -1763,10 +1763,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8351283895341867</v>
+        <v>95</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1782,14 +1782,14 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4157538359755651</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
@@ -1801,14 +1801,14 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1581013411205944</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E73" s="1" t="n">
@@ -1820,14 +1820,14 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6749962428236839</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E74" s="1" t="n">
@@ -1839,14 +1839,14 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2451594847046412</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E75" s="1" t="n">
@@ -1861,11 +1861,11 @@
         <v>31</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8488163244002824</v>
+        <v>52.6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E76" s="1" t="n">
@@ -1877,14 +1877,14 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7520387896134271</v>
+        <v>71.3</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E77" s="1" t="n">
@@ -1896,14 +1896,14 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6438990437118488</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E78" s="1" t="n">
@@ -1915,10 +1915,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3993522626638981</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1934,14 +1934,14 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2488590874633086</v>
+        <v>54</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E80" s="1" t="n">
@@ -1953,10 +1953,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6346208540301324</v>
+        <v>50.1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1972,14 +1972,14 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2766845984533768</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E82" s="1" t="n">
@@ -1991,14 +1991,14 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7789512462340464</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E83" s="1" t="n">
@@ -2010,14 +2010,14 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2173523522722004</v>
+        <v>62.1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E84" s="1" t="n">
@@ -2029,14 +2029,14 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9163554275696563</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E85" s="1" t="n">
@@ -2048,14 +2048,14 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9088557122075577</v>
+        <v>56</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E86" s="1" t="n">
@@ -2067,14 +2067,14 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8992307764643233</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E87" s="1" t="n">
@@ -2086,10 +2086,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C88" t="n">
-        <v>0.4653923024531237</v>
+        <v>64.3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2105,10 +2105,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C89" t="n">
-        <v>0.002343823803455325</v>
+        <v>58.1</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2124,14 +2124,14 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="C90" t="n">
-        <v>0.114240149367258</v>
+        <v>53</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E90" s="1" t="n">
@@ -2143,14 +2143,14 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C91" t="n">
-        <v>0.7833766446589623</v>
+        <v>69.5</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E91" s="1" t="n">
@@ -2162,14 +2162,14 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1386452732983616</v>
+        <v>68.5</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E92" s="1" t="n">
@@ -2181,10 +2181,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1562373265401166</v>
+        <v>61.2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2200,14 +2200,14 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3062339948986371</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E94" s="1" t="n">
@@ -2219,14 +2219,14 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8078354744967401</v>
+        <v>92.2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E95" s="1" t="n">
@@ -2238,14 +2238,14 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5456526728717797</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E96" s="1" t="n">
@@ -2257,14 +2257,14 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5706572036487262</v>
+        <v>97.8</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E97" s="1" t="n">
@@ -2276,14 +2276,14 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C98" t="n">
-        <v>0.9735247645652503</v>
+        <v>80</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E98" s="1" t="n">
@@ -2295,14 +2295,14 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9144781031086248</v>
+        <v>56.9</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E99" s="1" t="n">
@@ -2314,14 +2314,14 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7138110393467826</v>
+        <v>54.6</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E100" s="1" t="n">
@@ -2333,10 +2333,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7239460693745634</v>
+        <v>94.2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
